--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/24,06,26 Останкино КИ/машины Останкино КИ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/06,26/24,06,26 Останкино КИ/машины Останкино КИ.xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\Заказы на отправку и сортировку\Останкино\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\06,26\24,06,26 Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6CDD00-A118-4A9D-BB16-24B130925EB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8C8EDE-5657-464B-B2D3-F2CFD7CD64F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -781,12 +775,14 @@
       <c r="C7" s="12">
         <v>760</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7">
+        <v>3299</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2">
         <f t="shared" si="0"/>
-        <v>7181</v>
+        <v>3882</v>
       </c>
       <c r="H7">
         <v>1123</v>
@@ -803,12 +799,14 @@
       <c r="C8" s="12">
         <v>0</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7">
+        <v>5391</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-5391</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -823,11 +821,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2">
+        <v>8303</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>-8273</v>
       </c>
       <c r="I9">
         <v>29</v>
@@ -843,12 +843,14 @@
       <c r="C10" s="12">
         <v>560</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7">
+        <v>3094</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2">
         <f t="shared" si="0"/>
-        <v>6618</v>
+        <v>3524</v>
       </c>
       <c r="H10">
         <v>1019</v>
@@ -868,11 +870,11 @@
       <c r="C11" s="15"/>
       <c r="D11" s="8">
         <f>SUM(D2:D10)</f>
-        <v>3585</v>
+        <v>15369</v>
       </c>
       <c r="E11" s="4">
         <f>SUM(E2:E10)</f>
-        <v>0</v>
+        <v>8303</v>
       </c>
       <c r="F11" s="4">
         <f>SUM(F2:F10)</f>
@@ -880,7 +882,7 @@
       </c>
       <c r="G11" s="4">
         <f>SUM(G2:G10)</f>
-        <v>13829</v>
+        <v>-6258</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -894,11 +896,11 @@
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D14" s="3">
         <f>IF(ROUNDUP(D11/500,0)&gt;32,32,ROUNDUP(D11/500,0))</f>
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" ref="E14:F14" si="1">IF(ROUNDUP(E11/500,0)&gt;32,32,ROUNDUP(E11/500,0))</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="1"/>
